--- a/Source Data/Source_Data_Fig6.xlsx
+++ b/Source Data/Source_Data_Fig6.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samokeeffe/Documents/GitHub/abs-met-quant/Source Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02E735B-FEC2-6C4F-8B32-4EE5E2DD3B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F4EDBC-B25D-0442-A8D6-BF0537185FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="980" windowWidth="27640" windowHeight="15800" activeTab="4" xr2:uid="{7FC38D75-F77E-D949-9763-F8B4CEF1CFC9}"/>
+    <workbookView xWindow="780" yWindow="980" windowWidth="27640" windowHeight="15800" xr2:uid="{7FC38D75-F77E-D949-9763-F8B4CEF1CFC9}"/>
   </bookViews>
   <sheets>
-    <sheet name="6a" sheetId="1" r:id="rId1"/>
-    <sheet name="6b" sheetId="2" r:id="rId2"/>
-    <sheet name="6c" sheetId="3" r:id="rId3"/>
-    <sheet name="6g" sheetId="4" r:id="rId4"/>
-    <sheet name="6h" sheetId="5" r:id="rId5"/>
+    <sheet name="6A" sheetId="1" r:id="rId1"/>
+    <sheet name="6B" sheetId="2" r:id="rId2"/>
+    <sheet name="6C" sheetId="3" r:id="rId3"/>
+    <sheet name="6G" sheetId="4" r:id="rId4"/>
+    <sheet name="6H" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
